--- a/docs/files/REPORT_FILTRI/RZV - ANTONINI GABRIELE.xlsx
+++ b/docs/files/REPORT_FILTRI/RZV - ANTONINI GABRIELE.xlsx
@@ -684,13 +684,13 @@
         <v>25</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5025</v>
+        <v>4971</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4145</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1856</v>
+        <v>1830</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -838,19 +838,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>1827</v>
+        <v>1804</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1886</v>
+        <v>1847</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>555</v>
+        <v>545</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>1625</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>757</v>
@@ -859,14 +859,14 @@
         <v>179</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>815</v>
+        <v>801</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -897,19 +897,19 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>931</v>
+        <v>920</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>717</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>292</v>
@@ -918,7 +918,7 @@
         <v>203</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>144</v>
@@ -959,16 +959,16 @@
         <v>391</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>567</v>
+        <v>560</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>136</v>
@@ -977,7 +977,7 @@
         <v>71</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="N13" s="12" t="n">
         <v>15</v>
@@ -1015,19 +1015,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>221</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>73</v>
@@ -1036,7 +1036,7 @@
         <v>44</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N14" s="12" t="n">
         <v>10</v>
@@ -1077,16 +1077,16 @@
         <v>261</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>25</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>129</v>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1133,19 +1133,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>384</v>
+        <v>373</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>72</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>100</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>32</v>
@@ -1204,7 +1204,7 @@
         <v>22</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>98</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>43</v>
@@ -1213,14 +1213,14 @@
         <v>47</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>7</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>145</v>
@@ -1263,7 +1263,7 @@
         <v>73</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>50</v>
@@ -1272,10 +1272,10 @@
         <v>26</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>73</v>
@@ -1322,7 +1322,7 @@
         <v>0</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>113</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>31</v>
@@ -1369,19 +1369,19 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>29</v>
@@ -1390,7 +1390,7 @@
         <v>28</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>14</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>135</v>
+        <v>129</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>2</v>
@@ -1440,7 +1440,7 @@
         <v>10</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>19</v>
@@ -1449,10 +1449,10 @@
         <v>33</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>85</v>
@@ -1499,7 +1499,7 @@
         <v>0</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>14</v>
@@ -1508,14 +1508,14 @@
         <v>26</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>16</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1549,16 +1549,16 @@
         <v>75</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>7</v>
@@ -1567,10 +1567,10 @@
         <v>35</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>0</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>26</v>
@@ -1664,7 +1664,7 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>6</v>
@@ -1676,7 +1676,7 @@
         <v>2</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>17</v>
@@ -1685,7 +1685,7 @@
         <v>4</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>1</v>
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>50</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>11</v>
@@ -1744,7 +1744,7 @@
         <v>10</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>1</v>
@@ -1788,13 +1788,13 @@
         <v>0</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>12</v>
@@ -1841,7 +1841,7 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>118</v>
@@ -1853,7 +1853,7 @@
         <v>40</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>15</v>
@@ -1862,7 +1862,7 @@
         <v>8</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>20</v>
@@ -1903,16 +1903,16 @@
         <v>33</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>11</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>6</v>
@@ -1921,7 +1921,7 @@
         <v>13</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>19</v>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="H30" s="12" t="n">
         <v>11</v>
@@ -1971,7 +1971,7 @@
         <v>66</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>7</v>
@@ -1980,10 +1980,10 @@
         <v>7</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>0</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>3</v>
@@ -2077,10 +2077,10 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>1</v>
@@ -2089,7 +2089,7 @@
         <v>9</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>1</v>
@@ -2098,7 +2098,7 @@
         <v>0</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>1</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>4</v>
@@ -2148,7 +2148,7 @@
         <v>5</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>1</v>
@@ -2164,7 +2164,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
